--- a/Matrices2D.xlsx
+++ b/Matrices2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A7A922-746F-4E33-9DBF-1320179A0A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8EEF3-B7A5-4181-89CD-82897EBA62EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F671797E-0AEA-4698-B834-214E294FDDBB}"/>
   </bookViews>

--- a/Matrices2D.xlsx
+++ b/Matrices2D.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentGeorgeTolkach\Desktop\CG_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8EEF3-B7A5-4181-89CD-82897EBA62EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3A7755-C100-4F2C-A8CE-6F647A7961B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F671797E-0AEA-4698-B834-214E294FDDBB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -118,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,13 +278,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -311,31 +310,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -453,7 +440,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -544,16 +531,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4019237886466835</c:v>
+                  <c:v>-0.41421356237309503</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.0358983848622447</c:v>
+                  <c:v>-0.41421356237309515</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.4019237886466835</c:v>
+                  <c:v>0.99999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.7679491924311224</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -577,16 +564,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.5898384862245059E-2</c:v>
+                  <c:v>1.1102230246251565E-16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1.3301270189221936</c:v>
+                  <c:v>-1.4142135623730949</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.6961524227066325</c:v>
+                  <c:v>-1.4142135623730949</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.3301270189221937</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1349,8 +1336,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>107370</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -1369,7 +1356,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -1414,8 +1401,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>107370</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -1434,7 +1421,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -1479,8 +1466,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>57690</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Ink 6">
@@ -1499,7 +1486,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Ink 6">
@@ -1544,8 +1531,8 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>162165</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Ink 7">
@@ -1564,7 +1551,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Ink 7">
@@ -1609,8 +1596,8 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>50040</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Ink 8">
@@ -1629,7 +1616,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Ink 8">
@@ -1750,7 +1737,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1184 1 24575,'-18'1'0,"1"0"0,-1 2 0,1 0 0,0 1 0,0 0 0,0 2 0,-21 9 0,-109 63 0,71-35 0,-50 31 0,-170 132 0,281-195 0,-143 90 0,-10 7 0,140-83-1365,18-13-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">973 1 24575,'-15'1'0,"1"0"0,0 2 0,0 0 0,0 1 0,0 1 0,0 1 0,-17 9 0,-90 66 0,58-36 0,-40 32 0,-141 137 0,232-203 0,-118 94 0,-8 8 0,115-88-1365,15-12-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1804,7 +1791,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'18'11'0,"-1"1"0,0 0 0,-1 2 0,0 0 0,-1 1 0,20 25 0,-10-12 0,544 566 0,-492-507-1365,-60-68-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'13'11'0,"0"2"0,0-1 0,-1 3 0,-1-1 0,1 2 0,14 25 0,-8-12 0,405 584 0,-365-523-1365,-46-70-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1831,7 +1818,7 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">938 0 24575,'-23'18'0,"-16"15"0,-19 11 0,-10 16 0,-10 11 0,-6 7 0,-2 8 0,-4-1 0,8-2 0,9-10 0,9-14 0,10-7 0,10-13 0,12-8 0,7-5 0,4-3 0,5-4-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">938 0 24575,'-23'19'0,"-16"16"0,-19 12 0,-10 16 0,-10 12 0,-6 8 0,-2 8 0,-4-1 0,8-2 0,9-11 0,9-14 0,10-8 0,10-14 0,12-8 0,7-6 0,4-2 0,5-5-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -2153,75 +2140,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D671E20B-CB4A-4D66-8E0E-505ACE675FEC}">
   <dimension ref="A2:P48"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="6">
-        <v>0</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="6">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>-1</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="6">
-        <v>0</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>0</v>
+      </c>
+      <c r="B5" s="5">
         <v>-1</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="3"/>
       <c r="F5" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <f>RADIANS(G5)</f>
-        <v>0.52359877559829882</v>
+        <v>0.78539816339744828</v>
       </c>
       <c r="L5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4"/>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="F6" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>4</v>
       </c>
@@ -2229,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F11" s="2" t="s">
         <v>8</v>
       </c>
@@ -2264,113 +2251,112 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1">
+    <row r="12" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" thickTop="1">
-      <c r="A13" s="6">
+    <row r="13" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <f>A3</f>
         <v>0</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <f>B3</f>
         <v>1</v>
       </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="13">
-        <v>1</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0</v>
-      </c>
-      <c r="H13" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="6">
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <f t="shared" ref="A14:B14" si="0">A4</f>
         <v>-1</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="F14" s="16">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" thickBot="1">
-      <c r="A15" s="6">
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f t="shared" ref="A15:B15" si="1">A5</f>
         <v>0</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="18">
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16">
         <f>-G6</f>
-        <v>-3</v>
-      </c>
-      <c r="G15" s="19">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="2">
         <f>-I11</f>
         <v>-3</v>
       </c>
-      <c r="H15" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" thickTop="1">
-      <c r="A16" s="6">
+      <c r="H15" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <f t="shared" ref="A16:B16" si="2">A6</f>
         <v>1</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" cm="1">
         <f t="array" ref="A17:C20">MMULT(A13:C16,_xlfn.ANCHORARRAY(I45))</f>
-        <v>2.4019237886466835</v>
+        <v>-0.41421356237309503</v>
       </c>
       <c r="B17" s="2">
-        <v>3.5898384862245059E-2</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>1.1102230246251565E-16</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>2.0358983848622447</v>
+        <v>-0.41421356237309515</v>
       </c>
       <c r="B18" s="2">
-        <v>-1.3301270189221936</v>
-      </c>
-      <c r="C18" s="7">
+        <v>-1.4142135623730949</v>
+      </c>
+      <c r="C18" s="6">
         <v>1</v>
       </c>
       <c r="F18" t="s">
@@ -2380,67 +2366,67 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>3.4019237886466835</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="B19" s="2">
-        <v>-1.6961524227066325</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" thickBot="1">
+        <v>-1.4142135623730949</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>3.7679491924311224</v>
+        <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>-0.3301270189221937</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" thickTop="1">
-      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="12">
         <f>COS(K5)</f>
-        <v>0.86602540378443871</v>
+        <v>0.70710678118654757</v>
       </c>
       <c r="H21" s="2">
         <f>SIN(K5)</f>
-        <v>0.49999999999999994</v>
-      </c>
-      <c r="I21" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="G22" s="16">
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G22" s="14">
         <f>-SIN(K5)</f>
-        <v>-0.49999999999999994</v>
+        <v>-0.70710678118654746</v>
       </c>
       <c r="H22" s="2">
         <f>COS(K5)</f>
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="I22" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1">
-      <c r="G23" s="18">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G23" s="16">
         <v>0</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
       </c>
-      <c r="I23" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" thickTop="1"/>
-    <row r="25" spans="1:9">
+      <c r="I23" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
         <v>14</v>
       </c>
@@ -2451,267 +2437,267 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" thickBot="1"/>
-    <row r="28" spans="1:9" ht="15" thickTop="1">
-      <c r="G28" s="13">
+    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="12">
         <v>1</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
       </c>
-      <c r="I28" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="G29" s="16">
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G29" s="14">
         <v>0</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
       </c>
-      <c r="I29" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" thickBot="1">
-      <c r="G30" s="18">
+      <c r="I29" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G30" s="16">
         <f>G6</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="2">
         <f>H6</f>
-        <v>5</v>
-      </c>
-      <c r="I30" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" thickTop="1"/>
-    <row r="33" spans="7:15" ht="15" thickBot="1"/>
-    <row r="34" spans="7:15" ht="15" thickTop="1">
-      <c r="G34" s="40">
+        <v>0</v>
+      </c>
+      <c r="I30" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="7:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="G34" s="35">
         <f>F13</f>
         <v>1</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="9">
         <f>G13</f>
         <v>0</v>
       </c>
-      <c r="I34" s="37">
+      <c r="I34" s="32">
         <f t="shared" ref="I34" si="3">H13</f>
         <v>0</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="30">
         <f>G21</f>
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="K34" s="11">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="K34" s="10">
         <f t="shared" ref="K34:L36" si="4">H21</f>
-        <v>0.49999999999999994</v>
-      </c>
-      <c r="L34" s="33">
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="L34" s="28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="26">
         <f>G28</f>
         <v>1</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N34" s="11">
         <f t="shared" ref="N34:O36" si="5">H28</f>
         <v>0</v>
       </c>
-      <c r="O34" s="29">
+      <c r="O34" s="24">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="7:15">
-      <c r="G35" s="23">
+    <row r="35" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G35" s="18">
         <f>F14</f>
         <v>0</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="9">
         <f t="shared" ref="H35:I35" si="6">G14</f>
         <v>1</v>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="19">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="20">
         <f t="shared" ref="J35:J36" si="7">G22</f>
-        <v>-0.49999999999999994</v>
-      </c>
-      <c r="K35" s="11">
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="K35" s="10">
         <f t="shared" si="4"/>
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="L35" s="26">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="L35" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M35" s="27">
+      <c r="M35" s="22">
         <f t="shared" ref="M35:M36" si="8">G29</f>
         <v>0</v>
       </c>
-      <c r="N35" s="12">
+      <c r="N35" s="11">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O35" s="28">
+      <c r="O35" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="7:15" ht="15" thickBot="1">
-      <c r="G36" s="39">
+    <row r="36" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G36" s="34">
         <f>F15</f>
-        <v>-3</v>
-      </c>
-      <c r="H36" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H36" s="9">
         <f>-H30</f>
-        <v>-5</v>
-      </c>
-      <c r="I36" s="38">
+        <v>0</v>
+      </c>
+      <c r="I36" s="33">
         <f t="shared" ref="I36" si="9">H15</f>
         <v>1</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="31">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K36" s="11">
+      <c r="K36" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="29">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="27">
         <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="N36" s="12">
+        <v>1</v>
+      </c>
+      <c r="N36" s="11">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O36" s="30">
+        <v>0</v>
+      </c>
+      <c r="O36" s="25">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="7:15" ht="15" thickTop="1"/>
-    <row r="38" spans="7:15" ht="15" thickBot="1"/>
-    <row r="39" spans="7:15" ht="15" thickTop="1">
-      <c r="G39" s="47" cm="1">
+    <row r="37" spans="7:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="7:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="42" cm="1">
         <f t="array" ref="G39:I41">MMULT(G34:I36,J34:L36)</f>
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="H39" s="9">
-        <v>0.49999999999999994</v>
-      </c>
-      <c r="I39" s="45">
-        <v>0</v>
-      </c>
-      <c r="K39" s="31">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="H39" s="8">
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="I39" s="40">
+        <v>0</v>
+      </c>
+      <c r="K39" s="26">
         <f>M34</f>
         <v>1</v>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="11">
         <f t="shared" ref="L39:M41" si="10">N34</f>
         <v>0</v>
       </c>
-      <c r="M39" s="29">
+      <c r="M39" s="24">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="7:15">
-      <c r="G40" s="41">
-        <v>-0.49999999999999994</v>
-      </c>
-      <c r="H40" s="9">
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="I40" s="42">
-        <v>0</v>
-      </c>
-      <c r="K40" s="27">
+    <row r="40" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="G40" s="36">
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="H40" s="8">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="I40" s="37">
+        <v>0</v>
+      </c>
+      <c r="K40" s="22">
         <f t="shared" ref="K40:K41" si="11">M35</f>
         <v>0</v>
       </c>
-      <c r="L40" s="12">
+      <c r="L40" s="11">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="M40" s="28">
+      <c r="M40" s="23">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="7:15" ht="15" thickBot="1">
-      <c r="G41" s="48">
-        <v>-9.8076211353316456E-2</v>
-      </c>
-      <c r="H41" s="9">
-        <v>-5.8301270189221936</v>
-      </c>
-      <c r="I41" s="46">
-        <v>1</v>
-      </c>
-      <c r="K41" s="32">
+    <row r="41" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G41" s="43">
+        <v>-0.70710678118654757</v>
+      </c>
+      <c r="H41" s="8">
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="I41" s="41">
+        <v>1</v>
+      </c>
+      <c r="K41" s="27">
         <f t="shared" si="11"/>
-        <v>3</v>
-      </c>
-      <c r="L41" s="12">
+        <v>1</v>
+      </c>
+      <c r="L41" s="11">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="M41" s="30">
+        <v>0</v>
+      </c>
+      <c r="M41" s="25">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="7:15" ht="15" thickTop="1"/>
-    <row r="44" spans="7:15" ht="15" thickBot="1"/>
-    <row r="45" spans="7:15" ht="15" thickTop="1">
-      <c r="I45" s="49" cm="1">
+    <row r="42" spans="7:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="7:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I45" s="44" cm="1">
         <f t="array" ref="I45:K47">MMULT(_xlfn.ANCHORARRAY(G39),K39:M41)</f>
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="J45" s="8">
-        <v>0.49999999999999994</v>
-      </c>
-      <c r="K45" s="51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="7:15">
-      <c r="I46" s="43">
-        <v>-0.49999999999999994</v>
-      </c>
-      <c r="J46" s="8">
-        <v>0.86602540378443871</v>
-      </c>
-      <c r="K46" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="7:15" ht="15" thickBot="1">
-      <c r="I47" s="50">
-        <v>2.9019237886466835</v>
-      </c>
-      <c r="J47" s="8">
-        <v>-0.83012701892219365</v>
-      </c>
-      <c r="K47" s="52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="7:15" ht="15" thickTop="1"/>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="J45" s="7">
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="K45" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="7:15" x14ac:dyDescent="0.25">
+      <c r="I46" s="38">
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="J46" s="7">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="K46" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="7:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I47" s="45">
+        <v>0.29289321881345243</v>
+      </c>
+      <c r="J47" s="7">
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="K47" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="7:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
